--- a/events_prediction_dataset.xlsx
+++ b/events_prediction_dataset.xlsx
@@ -1,13 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\wetransfer_scouts_2026-02-06_2056\Scouts\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
   </bookViews>
@@ -19,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="57">
   <si>
     <t>event_id</t>
   </si>
@@ -187,12 +182,15 @@
   </si>
   <si>
     <t>GLJN</t>
+  </si>
+  <si>
+    <t>date_code</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -222,8 +220,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -526,14 +526,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:O11"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="38.33203125" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="13.77734375" customWidth="1"/>
+    <col min="4" max="4" width="32.77734375" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" customWidth="1"/>
+    <col min="6" max="6" width="17.21875" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" customWidth="1"/>
+    <col min="9" max="9" width="26" customWidth="1"/>
+    <col min="10" max="10" width="20.21875" customWidth="1"/>
+    <col min="13" max="13" width="15.6640625" customWidth="1"/>
+    <col min="14" max="14" width="22.88671875" customWidth="1"/>
+    <col min="15" max="15" width="12.44140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -576,8 +586,11 @@
       <c r="N1" t="s">
         <v>12</v>
       </c>
+      <c r="O1" s="2" t="s">
+        <v>56</v>
+      </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -620,8 +633,11 @@
       <c r="N2" t="b">
         <v>0</v>
       </c>
+      <c r="O2" s="1">
+        <v>30507</v>
+      </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -664,8 +680,11 @@
       <c r="N3" t="b">
         <v>0</v>
       </c>
+      <c r="O3" s="1">
+        <v>31792</v>
+      </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -708,8 +727,11 @@
       <c r="N4" t="b">
         <v>0</v>
       </c>
+      <c r="O4" s="1">
+        <v>33429</v>
+      </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -752,8 +774,11 @@
       <c r="N5" t="b">
         <v>1</v>
       </c>
+      <c r="O5" s="1">
+        <v>34890</v>
+      </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -796,8 +821,11 @@
       <c r="N6" t="b">
         <v>1</v>
       </c>
+      <c r="O6" s="1">
+        <v>35810</v>
+      </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -840,8 +868,11 @@
       <c r="N7" t="b">
         <v>1</v>
       </c>
+      <c r="O7" s="1">
+        <v>37271</v>
+      </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>33</v>
       </c>
@@ -884,8 +915,11 @@
       <c r="N8" t="b">
         <v>0</v>
       </c>
+      <c r="O8" s="1">
+        <v>39273</v>
+      </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>36</v>
       </c>
@@ -928,8 +962,11 @@
       <c r="N9" t="b">
         <v>0</v>
       </c>
+      <c r="O9" s="1">
+        <v>40734</v>
+      </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>39</v>
       </c>
@@ -972,8 +1009,11 @@
       <c r="N10" t="b">
         <v>0</v>
       </c>
+      <c r="O10" s="1">
+        <v>42195</v>
+      </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>42</v>
       </c>
@@ -1015,9 +1055,13 @@
       </c>
       <c r="N11" t="b">
         <v>0</v>
+      </c>
+      <c r="O11" s="1">
+        <v>43656</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>